--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008490899600580974</v>
       </c>
       <c r="C2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>39944212</v>
+        <v>4011143</v>
       </c>
       <c r="L2" t="n">
-        <v>21971514</v>
+        <v>1872783</v>
       </c>
       <c r="M2" t="n">
-        <v>5214613</v>
+        <v>370055</v>
       </c>
       <c r="N2" t="n">
-        <v>256152</v>
+        <v>9943</v>
       </c>
       <c r="O2" t="n">
-        <v>3078103</v>
+        <v>200268</v>
       </c>
       <c r="P2" t="n">
-        <v>1208734</v>
+        <v>75281</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999876618385315</v>
+        <v>0.9999861121177673</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8609394431114197</v>
+        <v>0.7591070532798767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7361105680465698</v>
+        <v>0.5672047138214111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6766498684883118</v>
+        <v>0.4582474827766418</v>
       </c>
       <c r="U2" t="n">
-        <v>0.264618456363678</v>
+        <v>0.06063433364033699</v>
       </c>
       <c r="V2" t="n">
-        <v>0.727166473865509</v>
+        <v>0.5051290392875671</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8199520707130432</v>
+        <v>0.6504769921302795</v>
       </c>
       <c r="X2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>43513679</v>
+        <v>4801660</v>
       </c>
       <c r="AG2" t="n">
-        <v>26954665</v>
+        <v>3018155</v>
       </c>
       <c r="AH2" t="n">
-        <v>7220207</v>
+        <v>805700</v>
       </c>
       <c r="AI2" t="n">
-        <v>532493</v>
+        <v>59334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4137274</v>
+        <v>460847</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9561951160430908</v>
+        <v>0.9551666378974915</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114695191383362</v>
+        <v>0.9119651317596436</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580380082130432</v>
+        <v>0.8582442998886108</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618042588233948</v>
+        <v>0.660926342010498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019699692726135</v>
+        <v>0.9019715189933777</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002032505781064863</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>39944212</v>
+        <v>4011143</v>
       </c>
       <c r="E3" t="n">
-        <v>5333597</v>
+        <v>960280</v>
       </c>
       <c r="F3" t="n">
-        <v>141419</v>
+        <v>37797</v>
       </c>
       <c r="G3" t="n">
-        <v>15286</v>
+        <v>3717</v>
       </c>
       <c r="H3" t="n">
-        <v>7821</v>
+        <v>2092</v>
       </c>
       <c r="I3" t="n">
-        <v>509</v>
+        <v>191</v>
       </c>
       <c r="J3" t="n">
-        <v>90625876</v>
+        <v>10069532</v>
       </c>
       <c r="K3" t="n">
-        <v>95849263</v>
+        <v>10127889</v>
       </c>
       <c r="L3" t="n">
-        <v>110242462</v>
+        <v>11668213</v>
       </c>
       <c r="M3" t="n">
-        <v>136829146</v>
+        <v>15037875</v>
       </c>
       <c r="N3" t="n">
-        <v>146226777</v>
+        <v>16172083</v>
       </c>
       <c r="O3" t="n">
-        <v>141999450</v>
+        <v>15708398</v>
       </c>
       <c r="P3" t="n">
-        <v>145737774</v>
+        <v>16181863</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8789983987808228</v>
+        <v>0.7997930645942688</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7416561245918274</v>
+        <v>0.5642962455749512</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6190957427024841</v>
+        <v>0.3934093415737152</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3180550634860992</v>
+        <v>0.1106289699673653</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6706628203392029</v>
+        <v>0.3916065990924835</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6943522691726685</v>
+        <v>0.3886754810810089</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43513679</v>
+        <v>4801660</v>
       </c>
       <c r="Z3" t="n">
-        <v>1789967</v>
+        <v>198183</v>
       </c>
       <c r="AA3" t="n">
-        <v>77049</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>61571</v>
+        <v>6873</v>
       </c>
       <c r="AC3" t="n">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90626580</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>100307692</v>
+        <v>11175395</v>
       </c>
       <c r="AG3" t="n">
-        <v>115500975</v>
+        <v>12805854</v>
       </c>
       <c r="AH3" t="n">
-        <v>138126469</v>
+        <v>15342287</v>
       </c>
       <c r="AI3" t="n">
-        <v>146666515</v>
+        <v>16295683</v>
       </c>
       <c r="AJ3" t="n">
-        <v>142704700</v>
+        <v>15854513</v>
       </c>
       <c r="AK3" t="n">
-        <v>145883883</v>
+        <v>16209047</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575468301773071</v>
+        <v>0.9574164748191833</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098641276359558</v>
+        <v>0.9094131588935852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572063446044922</v>
+        <v>0.8565481305122375</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611781120300293</v>
+        <v>0.6601688861846924</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901436984539032</v>
+        <v>0.9011460542678833</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03207146971768856</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>6027129</v>
+        <v>1165220</v>
       </c>
       <c r="E4" t="n">
-        <v>21971514</v>
+        <v>1872783</v>
       </c>
       <c r="F4" t="n">
-        <v>1385142</v>
+        <v>225637</v>
       </c>
       <c r="G4" t="n">
-        <v>96444</v>
+        <v>23589</v>
       </c>
       <c r="H4" t="n">
-        <v>131589</v>
+        <v>28182</v>
       </c>
       <c r="I4" t="n">
-        <v>13085</v>
+        <v>3364</v>
       </c>
       <c r="J4" t="n">
-        <v>704</v>
+        <v>88</v>
       </c>
       <c r="K4" t="n">
-        <v>6451864</v>
+        <v>1272885</v>
       </c>
       <c r="L4" t="n">
-        <v>7876603</v>
+        <v>1428993</v>
       </c>
       <c r="M4" t="n">
-        <v>2491903</v>
+        <v>437489</v>
       </c>
       <c r="N4" t="n">
-        <v>711853</v>
+        <v>154040</v>
       </c>
       <c r="O4" t="n">
-        <v>1154907</v>
+        <v>196201</v>
       </c>
       <c r="P4" t="n">
-        <v>265418</v>
+        <v>40451</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999938607215881</v>
+        <v>0.9999930262565613</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8698752522468567</v>
+        <v>0.7789191007614136</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7388729453086853</v>
+        <v>0.5657467246055603</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6465945839881897</v>
+        <v>0.423360288143158</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2888864278793335</v>
+        <v>0.0783345103263855</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6977726221084595</v>
+        <v>0.4411821067333221</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7519433498382568</v>
+        <v>0.4865974187850952</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1861428</v>
+        <v>210622</v>
       </c>
       <c r="Z4" t="n">
-        <v>26954665</v>
+        <v>3018155</v>
       </c>
       <c r="AA4" t="n">
-        <v>748119</v>
+        <v>83217</v>
       </c>
       <c r="AB4" t="n">
-        <v>49825</v>
+        <v>5601</v>
       </c>
       <c r="AC4" t="n">
-        <v>10286</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1993435</v>
+        <v>225379</v>
       </c>
       <c r="AG4" t="n">
-        <v>2618090</v>
+        <v>291352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1194580</v>
+        <v>133077</v>
       </c>
       <c r="AI4" t="n">
-        <v>272115</v>
+        <v>30440</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449657</v>
+        <v>50086</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568704962730408</v>
+        <v>0.9562901854515076</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106661081314087</v>
+        <v>0.9106873869895935</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576220273971558</v>
+        <v>0.857395350933075</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614910364151001</v>
+        <v>0.6605474352836609</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901703417301178</v>
+        <v>0.9015586376190186</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>297020</v>
+        <v>79814</v>
       </c>
       <c r="E5" t="n">
-        <v>2115232</v>
+        <v>364075</v>
       </c>
       <c r="F5" t="n">
-        <v>5214613</v>
+        <v>370055</v>
       </c>
       <c r="G5" t="n">
-        <v>232731</v>
+        <v>43653</v>
       </c>
       <c r="H5" t="n">
-        <v>511143</v>
+        <v>72416</v>
       </c>
       <c r="I5" t="n">
-        <v>52155</v>
+        <v>10603</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5498661</v>
+        <v>1004083</v>
       </c>
       <c r="L5" t="n">
-        <v>7653421</v>
+        <v>1446011</v>
       </c>
       <c r="M5" t="n">
-        <v>3208338</v>
+        <v>570581</v>
       </c>
       <c r="N5" t="n">
-        <v>549218</v>
+        <v>79934</v>
       </c>
       <c r="O5" t="n">
-        <v>1511540</v>
+        <v>311133</v>
       </c>
       <c r="P5" t="n">
-        <v>532074</v>
+        <v>118405</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999995231628418</v>
+        <v>0.9999946355819702</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9191132783889771</v>
+        <v>0.8612958192825317</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8948855996131897</v>
+        <v>0.8248657584190369</v>
       </c>
       <c r="T5" t="n">
-        <v>0.961418092250824</v>
+        <v>0.938592255115509</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9914644956588745</v>
+        <v>0.985747218132019</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9819522500038147</v>
+        <v>0.9690951704978943</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9946022033691406</v>
+        <v>0.9903231263160706</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72813</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>771695</v>
+        <v>86892</v>
       </c>
       <c r="AA5" t="n">
-        <v>7220207</v>
+        <v>805700</v>
       </c>
       <c r="AB5" t="n">
-        <v>89834</v>
+        <v>10028</v>
       </c>
       <c r="AC5" t="n">
-        <v>262705</v>
+        <v>29263</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1929194</v>
+        <v>213566</v>
       </c>
       <c r="AG5" t="n">
-        <v>2670270</v>
+        <v>300639</v>
       </c>
       <c r="AH5" t="n">
-        <v>1202744</v>
+        <v>134936</v>
       </c>
       <c r="AI5" t="n">
-        <v>272877</v>
+        <v>30543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452369</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734498262405396</v>
+        <v>0.9732611179351807</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642059206962585</v>
+        <v>0.9639381766319275</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837738275527954</v>
+        <v>0.9836736917495728</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963112473487854</v>
+        <v>0.9962851405143738</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938946962356567</v>
+        <v>0.993869423866272</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382031917572</v>
+        <v>0.998377799987793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>108780</v>
+        <v>19028</v>
       </c>
       <c r="E6" t="n">
-        <v>154915</v>
+        <v>25398</v>
       </c>
       <c r="F6" t="n">
-        <v>201589</v>
+        <v>26027</v>
       </c>
       <c r="G6" t="n">
-        <v>256152</v>
+        <v>9943</v>
       </c>
       <c r="H6" t="n">
-        <v>75552</v>
+        <v>8251</v>
       </c>
       <c r="I6" t="n">
-        <v>8274</v>
+        <v>1214</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58711</v>
+        <v>6601</v>
       </c>
       <c r="Z6" t="n">
-        <v>48403</v>
+        <v>5386</v>
       </c>
       <c r="AA6" t="n">
-        <v>98482</v>
+        <v>11048</v>
       </c>
       <c r="AB6" t="n">
-        <v>532493</v>
+        <v>59334</v>
       </c>
       <c r="AC6" t="n">
-        <v>62952</v>
+        <v>7027</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>18378</v>
+        <v>8539</v>
       </c>
       <c r="E7" t="n">
-        <v>251420</v>
+        <v>71485</v>
       </c>
       <c r="F7" t="n">
-        <v>715974</v>
+        <v>133775</v>
       </c>
       <c r="G7" t="n">
-        <v>334200</v>
+        <v>72238</v>
       </c>
       <c r="H7" t="n">
-        <v>3078103</v>
+        <v>200268</v>
       </c>
       <c r="I7" t="n">
-        <v>191395</v>
+        <v>25079</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7296</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267949</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68492</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4137274</v>
+        <v>460847</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>557</v>
+        <v>284</v>
       </c>
       <c r="E8" t="n">
-        <v>21439</v>
+        <v>7755</v>
       </c>
       <c r="F8" t="n">
-        <v>47779</v>
+        <v>14253</v>
       </c>
       <c r="G8" t="n">
-        <v>33192</v>
+        <v>10843</v>
       </c>
       <c r="H8" t="n">
-        <v>428802</v>
+        <v>85260</v>
       </c>
       <c r="I8" t="n">
-        <v>1208734</v>
+        <v>75281</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
